--- a/data/trans_orig/P25F_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P25F_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el modo de empleo para el que utilizan los cigarrillos electrónicos en 2023</t>
+          <t>Población según el modo de empleo para el que utilizan los cigarrillos electrónicos en 2023 (tasa de respuesta: 90,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1907</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>23,25%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>489</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1698</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>7487</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8124</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,49%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6428</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>498</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>7334</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>80,92%</t>
         </is>
       </c>
     </row>
@@ -1069,97 +1069,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1907</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>23,25%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>489</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>1698</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>3580</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,62 +1217,62 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>489</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3499</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>7,32%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>663</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3881</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>38,6%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11017</t>
+          <t>9859</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>659</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12132</t>
+          <t>11361</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18265</t>
+          <t>18998</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22476</t>
+          <t>21370</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50801</t>
+          <t>50901</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4007</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17273</t>
+          <t>17280</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31158</t>
+          <t>30493</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64269</t>
+          <t>65410</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>54,26%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23478</t>
+          <t>23688</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3621</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13711</t>
+          <t>13467</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10668</t>
+          <t>10760</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31007</t>
+          <t>30757</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23954</t>
+          <t>22239</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11415</t>
+          <t>11459</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7232</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29070</t>
+          <t>29545</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,51%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8779</t>
+          <t>9384</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29336</t>
+          <t>29408</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9068</t>
+          <t>9622</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23113</t>
+          <t>22632</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22329</t>
+          <t>21609</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>45663</t>
+          <t>47573</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>39,46%</t>
         </is>
       </c>
     </row>
@@ -2094,97 +2094,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2409</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2950</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>18,74%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>22,29%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>436</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2369</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>17,9%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>436</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2406</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12011</t>
+          <t>12070</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>776</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8563</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>7239</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18554</t>
+          <t>19344</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>74,14%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8622</t>
+          <t>8570</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9744</t>
+          <t>9553</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>36,61%</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6936</t>
+          <t>6386</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>591</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>7982</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,59%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>594</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6955</t>
+          <t>7529</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6314</t>
+          <t>6318</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10348</t>
+          <t>10761</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10631</t>
+          <t>10875</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13385</t>
+          <t>13723</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18604</t>
+          <t>17308</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>36048</t>
+          <t>34847</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>66550</t>
+          <t>63793</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7419</t>
+          <t>7628</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22233</t>
+          <t>22522</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>46507</t>
+          <t>48463</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>84055</t>
+          <t>84908</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>54,53%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25226</t>
+          <t>25223</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19171</t>
+          <t>19611</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16595</t>
+          <t>16171</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>39400</t>
+          <t>37925</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3631</t>
+          <t>3712</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25465</t>
+          <t>23690</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12828</t>
+          <t>13018</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9287</t>
+          <t>9314</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>30571</t>
+          <t>30126</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,35%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11946</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>32469</t>
+          <t>33297</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12004</t>
+          <t>12017</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>26716</t>
+          <t>27411</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>26126</t>
+          <t>26933</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>52429</t>
+          <t>53235</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>34,19%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25F_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P25F_2023-Estudios-trans_orig.xlsx
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7487</t>
+          <t>8683</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>386</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>935</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>907</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>8918</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>81,59%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>4582</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6568</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>549</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>935</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7334</t>
+          <t>9223</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>84,38%</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>855</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>855</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3499</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>43,09%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>9996</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>9996</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>9996</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>935</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>935</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>935</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t>10931</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t>10931</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t>10931</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9859</t>
+          <t>9811</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>655</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11361</t>
+          <t>12637</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7993</t>
+          <t>7729</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2977</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18998</t>
+          <t>19089</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36736</t>
+          <t>39134</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21370</t>
+          <t>25357</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50901</t>
+          <t>52289</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9324</t>
+          <t>11891</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>5938</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17280</t>
+          <t>21108</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>46061</t>
+          <t>51026</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30493</t>
+          <t>36221</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>65410</t>
+          <t>68412</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>50,41%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11678</t>
+          <t>13407</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5505</t>
+          <t>5848</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23688</t>
+          <t>24826</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7223</t>
+          <t>7831</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13467</t>
+          <t>14602</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>18901</t>
+          <t>21238</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10760</t>
+          <t>12368</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>30757</t>
+          <t>32452</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9033</t>
+          <t>9650</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22239</t>
+          <t>21916</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>9428</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>16907</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>14534</t>
+          <t>19078</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>11099</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29545</t>
+          <t>33995</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>25,05%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>17413</t>
+          <t>19406</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9384</t>
+          <t>10061</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29408</t>
+          <t>31497</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>15650</t>
+          <t>17228</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9622</t>
+          <t>10643</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22632</t>
+          <t>25432</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>33063</t>
+          <t>36634</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21609</t>
+          <t>25435</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47573</t>
+          <t>50918</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>37,52%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>78658</t>
+          <t>85301</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>78658</t>
+          <t>85301</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>78658</t>
+          <t>85301</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41893</t>
+          <t>50403</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>41893</t>
+          <t>50403</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>41893</t>
+          <t>50403</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>120552</t>
+          <t>135704</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>120552</t>
+          <t>135704</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>120552</t>
+          <t>135704</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>456</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2950</t>
+          <t>2985</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>456</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>12,66%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12070</t>
+          <t>12271</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>907</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8155</t>
+          <t>9014</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>12998</t>
+          <t>13791</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7239</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19344</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>71,99%</t>
         </is>
       </c>
     </row>
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4411</t>
+          <t>4874</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>1761</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8570</t>
+          <t>9069</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>4411</t>
+          <t>4874</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9553</t>
+          <t>10851</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>38,87%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6386</t>
+          <t>5814</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>4897</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>644</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>7816</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>27,99%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2717</t>
+          <t>3041</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>674</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7529</t>
+          <t>8244</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2894</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>851</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6318</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>5611</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2621,22 +2621,22 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10761</t>
+          <t>11283</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>40,41%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12857</t>
+          <t>13263</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12857</t>
+          <t>13263</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12857</t>
+          <t>13263</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13236</t>
+          <t>14657</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13236</t>
+          <t>14657</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13236</t>
+          <t>14657</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>26093</t>
+          <t>27920</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>26093</t>
+          <t>27920</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>26093</t>
+          <t>27920</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10875</t>
+          <t>10948</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1374</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13723</t>
+          <t>12983</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>8185</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17308</t>
+          <t>17127</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>50461</t>
+          <t>52694</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34847</t>
+          <t>36655</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>63793</t>
+          <t>67000</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>13818</t>
+          <t>17068</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7628</t>
+          <t>9132</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22522</t>
+          <t>25710</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>64279</t>
+          <t>69762</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>48463</t>
+          <t>52095</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>84908</t>
+          <t>88732</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>50,83%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>14362</t>
+          <t>17988</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>9700</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25223</t>
+          <t>29336</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>12130</t>
+          <t>13254</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>7673</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19611</t>
+          <t>21268</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>26492</t>
+          <t>31242</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>20258</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>37925</t>
+          <t>45504</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10872</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23690</t>
+          <t>23850</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>10890</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>5490</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13018</t>
+          <t>18830</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>17170</t>
+          <t>21762</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>12426</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>30126</t>
+          <t>34659</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>20793</t>
+          <t>23302</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11823</t>
+          <t>14660</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>33297</t>
+          <t>35994</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>18544</t>
+          <t>20303</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12017</t>
+          <t>13900</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>27411</t>
+          <t>29584</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>39337</t>
+          <t>43605</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>26933</t>
+          <t>30701</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>53235</t>
+          <t>58207</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>33,35%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>99719</t>
+          <t>108560</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>99719</t>
+          <t>108560</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>99719</t>
+          <t>108560</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>55989</t>
+          <t>65995</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>55989</t>
+          <t>65995</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>55989</t>
+          <t>65995</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>155708</t>
+          <t>174555</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>155708</t>
+          <t>174555</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>155708</t>
+          <t>174555</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
